--- a/excel/Lendermarket Rima.xlsx
+++ b/excel/Lendermarket Rima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Lendermarket\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5884C0C5-C246-4D34-A5A4-D926C2F95973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9304FA57-8A3C-4A04-8804-8A3973C5ECBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -464,27 +464,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -504,6 +483,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2501,43 +2501,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="32" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32" t="s">
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="Q1" s="26" t="s">
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="Q1" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="26" t="s">
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="V1" s="28"/>
-      <c r="W1" s="29" t="s">
+      <c r="V1" s="39"/>
+      <c r="W1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="31"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
       <c r="AA1" s="4" t="s">
         <v>31</v>
       </c>
@@ -2589,10 +2589,10 @@
         <v>31</v>
       </c>
       <c r="P2" s="8"/>
-      <c r="Q2" s="35" t="s">
+      <c r="Q2" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="R2" s="35" t="s">
+      <c r="R2" s="28" t="s">
         <v>7</v>
       </c>
       <c r="S2" s="4" t="s">
@@ -2601,10 +2601,10 @@
       <c r="T2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="U2" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="V2" s="36" t="s">
+      <c r="U2" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="V2" s="29" t="s">
         <v>1</v>
       </c>
       <c r="W2" s="4" t="s">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="K3" s="15">
         <f ca="1">'553f164f3402'!B12</f>
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="L3" s="15" t="str">
         <f ca="1">'553f164f3402'!P3</f>
@@ -2687,47 +2687,47 @@
         <v>0</v>
       </c>
       <c r="P3" s="9"/>
-      <c r="Q3" s="37">
+      <c r="Q3" s="30">
         <f>Pinigai!I2</f>
         <v>80</v>
       </c>
-      <c r="R3" s="37">
+      <c r="R3" s="30">
         <f>SUM(H3:H100)-U3</f>
-        <v>92.100000000000009</v>
-      </c>
-      <c r="S3" s="38">
+        <v>87.720000000000013</v>
+      </c>
+      <c r="S3" s="31">
         <f>Pinigai!H2</f>
         <v>10.45</v>
       </c>
-      <c r="T3" s="37">
+      <c r="T3" s="30">
         <f>W3-R3</f>
-        <v>0</v>
-      </c>
-      <c r="U3" s="37">
+        <v>4.5699999999999932</v>
+      </c>
+      <c r="U3" s="30">
         <f>SUM(M3:M100)</f>
-        <v>104.80999999999999</v>
-      </c>
-      <c r="V3" s="37">
+        <v>109.18999999999998</v>
+      </c>
+      <c r="V3" s="30">
         <f>SUM(N3:N100)-AA3</f>
-        <v>1.65</v>
+        <v>1.8400000000000003</v>
       </c>
       <c r="W3" s="3">
         <f>Q3+S3+V3</f>
-        <v>92.100000000000009</v>
+        <v>92.29</v>
       </c>
       <c r="X3" s="3">
         <f>W3-Q3</f>
-        <v>12.100000000000009</v>
+        <v>12.290000000000006</v>
       </c>
       <c r="Y3" s="7">
         <f>(W3-Q3)/Q3</f>
-        <v>0.15125000000000011</v>
-      </c>
-      <c r="Z3" s="39">
+        <v>0.15362500000000007</v>
+      </c>
+      <c r="Z3" s="32">
         <f ca="1">XIRR(Pinigai!K3:K200,Pinigai!A3:A200)</f>
-        <v>0.89048351049423213</v>
-      </c>
-      <c r="AA3" s="37">
+        <v>0.82542220354080209</v>
+      </c>
+      <c r="AA3" s="30">
         <f>SUM(O3:O100)</f>
         <v>0</v>
       </c>
@@ -2797,17 +2797,17 @@
         <v>0</v>
       </c>
       <c r="P4" s="9"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="33"/>
-      <c r="S4" s="33"/>
-      <c r="T4" s="33"/>
-      <c r="U4" s="33"/>
-      <c r="V4" s="33"/>
-      <c r="W4" s="33"/>
-      <c r="X4" s="33"/>
-      <c r="Y4" s="34"/>
-      <c r="Z4" s="34"/>
-      <c r="AA4" s="34"/>
+      <c r="Q4" s="26"/>
+      <c r="R4" s="26"/>
+      <c r="S4" s="26"/>
+      <c r="T4" s="26"/>
+      <c r="U4" s="26"/>
+      <c r="V4" s="26"/>
+      <c r="W4" s="26"/>
+      <c r="X4" s="26"/>
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="27"/>
+      <c r="AA4" s="27"/>
       <c r="AC4" s="3" t="str">
         <f ca="1">'8945000DP4C3YFA45N3405281774'!Z3</f>
         <v/>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K5" s="15">
         <f ca="1">'8945000DP4C3YFA45N3421733887'!B12</f>
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="L5" s="15" t="str">
         <f ca="1">'8945000DP4C3YFA45N3421733887'!P3</f>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="K6" s="15">
         <f ca="1">'8945000DP4C3YFA45N3429182335'!B12</f>
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="L6" s="15" t="str">
         <f ca="1">'8945000DP4C3YFA45N3429182335'!P3</f>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="K7" s="15">
         <f ca="1">'8945000DP4C3YFA45N3420270580'!B12</f>
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L7" s="15" t="str">
         <f ca="1">'8945000DP4C3YFA45N3420270580'!P3</f>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="K11" s="15">
         <f ca="1">'8945000DP4C3YFA45N3465337173'!B12</f>
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="L11" s="15" t="str">
         <f ca="1">'8945000DP4C3YFA45N3465337173'!P3</f>
@@ -3259,11 +3259,11 @@
       </c>
       <c r="M11" s="3">
         <f>'8945000DP4C3YFA45N3465337173'!K3</f>
-        <v>5.76</v>
+        <v>8.65</v>
       </c>
       <c r="N11" s="3">
         <f>'8945000DP4C3YFA45N3465337173'!L3</f>
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="O11" s="3">
         <f>'8945000DP4C3YFA45N3465337173'!M3</f>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="K13" s="15">
         <f ca="1">'8945000DP4C3YFA45N3455363691'!B12</f>
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L13" s="15" t="str">
         <f ca="1">'8945000DP4C3YFA45N3455363691'!P3</f>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="K14" s="15">
         <f ca="1">'8945000DP4C3YFA45N3453716086'!B12</f>
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="L14" s="15" t="str">
         <f ca="1">'8945000DP4C3YFA45N3453716086'!P3</f>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="K15" s="15">
         <f ca="1">'8945000DP4C3YFA45N3468426074'!B12</f>
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="L15" s="15" t="str">
         <f ca="1">'8945000DP4C3YFA45N3468426074'!P3</f>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="K16" s="15">
         <f ca="1">'8945000DP4C3YFA45N3448669708'!B12</f>
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="L16" s="15" t="str">
         <f ca="1">'8945000DP4C3YFA45N3448669708'!P3</f>
@@ -3579,11 +3579,11 @@
       </c>
       <c r="M16" s="3">
         <f>'8945000DP4C3YFA45N3448669708'!K3</f>
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="N16" s="3">
         <f>'8945000DP4C3YFA45N3448669708'!L3</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="O16" s="3">
         <f>'8945000DP4C3YFA45N3448669708'!M3</f>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="K17" s="15">
         <f ca="1">'8945000DP4C3YFA45N3475977996'!B12</f>
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="L17" s="15" t="str">
         <f ca="1">'8945000DP4C3YFA45N3475977996'!P3</f>
@@ -3835,12 +3835,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="W1:Z1"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="I1:L1"/>
     <mergeCell ref="M1:O1"/>
     <mergeCell ref="Q1:T1"/>
     <mergeCell ref="U1:V1"/>
-    <mergeCell ref="W1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:O27">
     <cfRule type="expression" dxfId="63" priority="11">
@@ -3909,29 +3909,29 @@
       <c r="B1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="30"/>
-      <c r="I1" s="31"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="31"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -5214,29 +5214,29 @@
       <c r="B1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="30"/>
-      <c r="I1" s="31"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="31"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -6499,29 +6499,29 @@
       <c r="B1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="30"/>
-      <c r="I1" s="31"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="31"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -7784,29 +7784,29 @@
       <c r="B1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="30"/>
-      <c r="I1" s="31"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="31"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="B12" s="15">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -9089,29 +9089,29 @@
       <c r="B1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="30"/>
-      <c r="I1" s="31"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="31"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="B12" s="15">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -10404,29 +10404,29 @@
       <c r="B1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="30"/>
-      <c r="I1" s="31"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="31"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="B12" s="15">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -11721,29 +11721,29 @@
       <c r="B1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="30"/>
-      <c r="I1" s="31"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="31"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -13006,29 +13006,29 @@
       <c r="B1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="30"/>
-      <c r="I1" s="31"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="31"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -13389,7 +13389,7 @@
       </c>
       <c r="B12" s="15">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -15816,14 +15816,14 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="23">
         <f ca="1">TODAY()</f>
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
       <c r="K200" s="3">
         <f>Overview!W3</f>
-        <v>92.100000000000009</v>
+        <v>92.29</v>
       </c>
     </row>
   </sheetData>
@@ -15858,29 +15858,29 @@
       <c r="B1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="30"/>
-      <c r="I1" s="31"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="31"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -16203,7 +16203,7 @@
       </c>
       <c r="B12" s="15">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -17132,29 +17132,29 @@
       <c r="B1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="30"/>
-      <c r="I1" s="31"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="31"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -17223,22 +17223,30 @@
       <c r="D3" s="10">
         <v>46239</v>
       </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="15" t="str">
+      <c r="E3" s="10">
+        <v>46241</v>
+      </c>
+      <c r="F3" s="15">
         <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1.49</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="L3" s="3">
         <f>H53-I53</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -17293,11 +17301,11 @@
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>0</v>
+        <v>46241</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>0</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -17477,7 +17485,7 @@
       </c>
       <c r="B12" s="15">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -18337,11 +18345,11 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -18409,29 +18417,29 @@
       <c r="B1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="30"/>
-      <c r="I1" s="31"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="31"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -18754,7 +18762,7 @@
       </c>
       <c r="B12" s="15">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -19686,29 +19694,29 @@
       <c r="B1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="30"/>
-      <c r="I1" s="31"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="31"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -20039,7 +20047,7 @@
       </c>
       <c r="B12" s="15">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -20971,29 +20979,29 @@
       <c r="B1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="30"/>
-      <c r="I1" s="31"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="31"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -21324,7 +21332,7 @@
       </c>
       <c r="B12" s="15">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -22256,29 +22264,29 @@
       <c r="B1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="30"/>
-      <c r="I1" s="31"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="31"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -23551,29 +23559,29 @@
       <c r="B1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="30"/>
-      <c r="I1" s="31"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="31"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -23661,11 +23669,11 @@
       <c r="J3" s="13"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>5.76</v>
+        <v>8.65</v>
       </c>
       <c r="L3" s="3">
         <f>H53-I53</f>
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -23740,15 +23748,25 @@
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="6"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="15" t="str">
+      <c r="D5" s="10">
+        <v>46243</v>
+      </c>
+      <c r="E5" s="10">
+        <v>46242</v>
+      </c>
+      <c r="F5" s="15">
         <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
-        <v/>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+        <v>-1</v>
+      </c>
+      <c r="G5" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.11</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
       <c r="J5" s="9"/>
       <c r="X5" s="6">
         <f t="shared" ref="X5:X52" si="1">E4</f>
@@ -23774,11 +23792,11 @@
       <c r="J6" s="9"/>
       <c r="X6" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46242</v>
       </c>
       <c r="Y6" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -23914,7 +23932,7 @@
       </c>
       <c r="B12" s="15">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="6"/>
@@ -24774,11 +24792,11 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>5.76</v>
+        <v>8.65</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
